--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104732_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104732_W31.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1172</v>
+        <v>7.0724</v>
       </c>
       <c r="E2" t="n">
-        <v>7.372</v>
+        <v>6.9878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7452</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4346</v>
+        <v>2.4313</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5598</v>
+        <v>1.5569</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8748</v>
+        <v>0.8744</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6322</v>
+        <v>4.6121</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1596</v>
+        <v>4.1434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4727</v>
+        <v>0.4687</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1976</v>
+        <v>-2.1808</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5998</v>
+        <v>-2.5864</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4021</v>
+        <v>0.4057</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5232</v>
+        <v>0.4833</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3979</v>
+        <v>0.039</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1254</v>
+        <v>0.4443</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7133</v>
+        <v>5.6418</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8385</v>
+        <v>5.6873</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1252</v>
+        <v>-0.0455</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5367</v>
+        <v>4.5267</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9264</v>
+        <v>0.9224</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6103</v>
+        <v>3.6043</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1107</v>
+        <v>6.0893</v>
       </c>
       <c r="K3" t="n">
-        <v>2.587</v>
+        <v>2.5748</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5237</v>
+        <v>3.5145</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.574</v>
+        <v>-1.5626</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6605</v>
+        <v>-1.6524</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8116</v>
+        <v>0.7572</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.8335</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1416</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4101</v>
+        <v>4.6946</v>
       </c>
       <c r="E4" t="n">
-        <v>4.619</v>
+        <v>4.6024</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2088</v>
+        <v>0.0922</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5011</v>
+        <v>3.4998</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1451</v>
+        <v>-1.1432</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6462</v>
+        <v>4.643</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5907</v>
+        <v>5.5782</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9738</v>
+        <v>0.9685</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6169</v>
+        <v>4.6097</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0895</v>
+        <v>-2.0784</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1188</v>
+        <v>-2.1117</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0293</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0902</v>
+        <v>0.1917</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1642</v>
+        <v>0.1623</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2545</v>
+        <v>0.0294</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9992</v>
+        <v>1.0032</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9992</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5587</v>
+        <v>-0.4125</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7492</v>
+        <v>-0.5135</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1904</v>
+        <v>0.101</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9821</v>
+        <v>-0.9805</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0045</v>
+        <v>0.0056</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9866</v>
+        <v>-0.9861</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6798</v>
+        <v>-0.6807</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3023</v>
+        <v>-0.2998</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2582</v>
+        <v>-0.1149</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0694</v>
+        <v>0.1672</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1888</v>
+        <v>-0.2821</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6774</v>
+        <v>-1.5714</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1821</v>
+        <v>-0.2703</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8594</v>
+        <v>-1.301</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0296</v>
+        <v>-1.8098</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5169</v>
+        <v>-1.6147</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4873</v>
+        <v>-0.1952</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3678</v>
+        <v>-0.2168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6221</v>
+        <v>-0.1346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7456</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3382</v>
+        <v>-1.5931</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1052</v>
+        <v>-1.48</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2329</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1571</v>
+        <v>-0.238</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9503</v>
+        <v>-0.0049</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2068</v>
+        <v>-0.2331</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1825</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1825</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9331</v>
+        <v>-1.8593</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0238</v>
+        <v>1.1118</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9093</v>
+        <v>-2.9711</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.815</v>
+        <v>0.0341</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6199</v>
+        <v>0.5194</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1951</v>
+        <v>-0.4854</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2128</v>
+        <v>1.3653</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1322</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0806</v>
+        <v>0.7447</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6022</v>
+        <v>-1.3312</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4877</v>
+        <v>-0.1011</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1145</v>
+        <v>-1.2301</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4544</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4044</v>
+        <v>0.9685</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2336</v>
+        <v>0.8847</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1708</v>
+        <v>0.0838</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9318</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1594</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.839</v>
+        <v>-2.9949</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4276</v>
+        <v>0.1472</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4114</v>
+        <v>-3.1421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3099</v>
+        <v>0.3105</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1992</v>
+        <v>-2.1947</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5092</v>
+        <v>2.5052</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3995</v>
+        <v>2.3889</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0804</v>
+        <v>-0.0829</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4799</v>
+        <v>2.4719</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0895</v>
+        <v>-2.0784</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1188</v>
+        <v>-2.1117</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0293</v>
+        <v>0.0333</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8305</v>
+        <v>0.0117</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5553</v>
+        <v>0.0346</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2753</v>
+        <v>-0.0229</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2895</v>
+        <v>-4.6457</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2582</v>
+        <v>-1.3497</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0313</v>
+        <v>-3.296</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1936</v>
+        <v>-1.2981</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8754</v>
+        <v>-2.8068</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3182</v>
+        <v>1.5087</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6365</v>
+        <v>1.1829</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7483</v>
+        <v>-0.9243</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1118</v>
+        <v>2.1072</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5571</v>
+        <v>-2.4809</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1271</v>
+        <v>-1.8825</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4301</v>
+        <v>-0.5984</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4544</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3909</v>
+        <v>-0.9802</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4858</v>
+        <v>-0.5718</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.905</v>
+        <v>-0.4085</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2507</v>
+        <v>-0.7739</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2507</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4924</v>
+        <v>-5.0714</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8022</v>
+        <v>-2.5934</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.6902</v>
+        <v>-2.4779</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3034</v>
+        <v>-1.2539</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8146</v>
+        <v>-0.4835</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5112</v>
+        <v>-0.7704</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1919</v>
+        <v>1.4415</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9211</v>
+        <v>1.2411</v>
       </c>
       <c r="L11" t="n">
-        <v>2.113</v>
+        <v>0.2004</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4953</v>
+        <v>-2.6954</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8935</v>
+        <v>-1.7246</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6018</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5903</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8263</v>
+        <v>-0.6306</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0411</v>
+        <v>-0.5718</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7852</v>
+        <v>-0.0589</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7724</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3188</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.825</v>
+        <v>-5.2234</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0437</v>
+        <v>-2.2663</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7813</v>
+        <v>-2.9571</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2604</v>
+        <v>-2.1899</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4914</v>
+        <v>-1.8728</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7689</v>
+        <v>-0.3172</v>
       </c>
       <c r="J12" t="n">
-        <v>1.45</v>
+        <v>-0.6402</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2443</v>
+        <v>-0.7519</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2057</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7103</v>
+        <v>-1.5497</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7357</v>
+        <v>-1.1209</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9746</v>
+        <v>-0.4289</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.1806</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5437</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3839</v>
+        <v>-1.3309</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0411</v>
+        <v>-0.4879</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3428</v>
+        <v>-0.843</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7376</v>
+        <v>-2.735599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>13.3438</v>
+        <v>13.1775</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.0813</v>
+        <v>-15.9129</v>
       </c>
       <c r="G13" t="n">
-        <v>3.257400000000001</v>
+        <v>3.2702</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.137999999999999</v>
+        <v>-7.1114</v>
       </c>
       <c r="I13" t="n">
-        <v>10.3956</v>
+        <v>10.3813</v>
       </c>
       <c r="J13" t="n">
-        <v>21.2137</v>
+        <v>21.1205</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7394</v>
+        <v>7.689100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>13.4744</v>
+        <v>13.4315</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.956</v>
+        <v>-17.8503</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.8772</v>
+        <v>-14.8002</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.0789</v>
+        <v>-3.0501</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.8156</v>
+        <v>-6.829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0389</v>
+        <v>-17.0725</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2235</v>
+        <v>10.2436</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8836999999999997</v>
+        <v>-0.8822000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5064000000000006</v>
+        <v>0.4849</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3902</v>
+        <v>-1.3673</v>
       </c>
       <c r="V13" t="n">
-        <v>1.704199999999999</v>
+        <v>1.7058</v>
       </c>
       <c r="W13" t="n">
-        <v>8.662699999999999</v>
+        <v>8.644299999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.958500000000001</v>
+        <v>-6.9386</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0512</v>
+        <v>5.9185</v>
       </c>
       <c r="E14" t="n">
-        <v>8.0937</v>
+        <v>7.0061</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0425</v>
+        <v>-1.0875</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7357</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0766</v>
+        <v>-0.0825</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6591</v>
+        <v>-0.6549</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2845</v>
+        <v>2.2713</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5389</v>
+        <v>1.5266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7456</v>
+        <v>0.7447</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0201</v>
+        <v>-3.0087</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6154</v>
+        <v>-1.6091</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4047</v>
+        <v>-1.3997</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5362</v>
+        <v>0.4087</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8304</v>
+        <v>0.7638</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2943</v>
+        <v>-0.3551</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9788</v>
+        <v>3.9709</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9788</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.935</v>
+        <v>3.8934</v>
       </c>
       <c r="E15" t="n">
-        <v>3.033</v>
+        <v>3.6039</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.098</v>
+        <v>0.2895</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2429</v>
+        <v>3.2343</v>
       </c>
       <c r="H15" t="n">
-        <v>2.741</v>
+        <v>2.7323</v>
       </c>
       <c r="I15" t="n">
         <v>0.502</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4806</v>
+        <v>4.4641</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8462</v>
+        <v>2.8334</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2376</v>
+        <v>-1.2298</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1052</v>
+        <v>-0.1011</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1324</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8986</v>
+        <v>0.0673</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6751</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2235</v>
+        <v>0.1535</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6489</v>
+        <v>2.0537</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0086</v>
+        <v>3.4569</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3597</v>
+        <v>-1.4032</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9602</v>
+        <v>2.9502</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0016</v>
+        <v>0.9946</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9586</v>
+        <v>1.9556</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9585</v>
+        <v>4.9392</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2796</v>
+        <v>1.2681</v>
       </c>
       <c r="L16" t="n">
-        <v>3.6789</v>
+        <v>3.6711</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9983</v>
+        <v>-1.989</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.278</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2878</v>
+        <v>0.1231</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8139</v>
+        <v>-0.3441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5261</v>
+        <v>0.4672</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6224</v>
+        <v>1.9978</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4342</v>
+        <v>2.0114</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1882</v>
+        <v>-0.0136</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0076</v>
+        <v>0.0061</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6121</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6078</v>
+        <v>-0.6061</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1787</v>
+        <v>2.1674</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0662</v>
+        <v>1.058</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1124</v>
+        <v>1.1094</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1711</v>
+        <v>-2.1613</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4508</v>
+        <v>-0.4458</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0245</v>
+        <v>0.3984</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.156</v>
       </c>
       <c r="U17" t="n">
-        <v>0.769</v>
+        <v>0.5543</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8514</v>
+        <v>0.4606</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1775</v>
+        <v>-0.4212</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0289</v>
+        <v>0.8818</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.637</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0128</v>
+        <v>-0.0116</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6278</v>
+        <v>-0.6254</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5242</v>
+        <v>-0.5256</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5988</v>
+        <v>-0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1163</v>
+        <v>-0.1114</v>
       </c>
       <c r="N18" t="n">
-        <v>0.586</v>
+        <v>0.5884</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7023</v>
+        <v>-0.6998</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8551</v>
+        <v>0.4634</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3914</v>
+        <v>0.1531</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4637</v>
+        <v>0.3104</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2353</v>
+        <v>0.0667</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1578</v>
+        <v>0.9133</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9225</v>
+        <v>-0.8466</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0525</v>
+        <v>-2.0471</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2457</v>
+        <v>-0.2418</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8068</v>
+        <v>-1.8053</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6421</v>
+        <v>-0.6449</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1901</v>
+        <v>0.1896</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8345</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4104</v>
+        <v>-1.4022</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4358</v>
+        <v>-0.4314</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1666</v>
+        <v>-0.3414</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5492</v>
+        <v>0.311</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7158</v>
+        <v>-0.6524</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1996,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0634</v>
+        <v>-0.4001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7037</v>
+        <v>1.1649</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7671</v>
+        <v>-1.5651</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3383</v>
+        <v>0.3386</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5793</v>
+        <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.241</v>
+        <v>-0.2414</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2371</v>
+        <v>2.229</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5035</v>
+        <v>1.4996</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7336</v>
+        <v>0.7294</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8988</v>
+        <v>-1.8904</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9242</v>
+        <v>-0.9196</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2192</v>
+        <v>-0.5598</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3975</v>
+        <v>0.0741</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8218</v>
+        <v>-0.6339</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5483</v>
+        <v>-1.6323</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4219</v>
+        <v>0.8789</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9702</v>
+        <v>-2.5112</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1985</v>
+        <v>-1.1934</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0774</v>
+        <v>-0.075</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1211</v>
+        <v>-1.1184</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9794</v>
+        <v>1.9733</v>
       </c>
       <c r="K22" t="n">
-        <v>1.538</v>
+        <v>1.5341</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4414</v>
+        <v>0.4392</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1779</v>
+        <v>-3.1667</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6154</v>
+        <v>-1.6091</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5625</v>
+        <v>-1.5576</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1226</v>
+        <v>-0.2113</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5363</v>
+        <v>-0.0653</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4137</v>
+        <v>-0.146</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2186</v>
+        <v>-2.4082</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2475</v>
+        <v>0.3256</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.971</v>
+        <v>-2.7338</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4717</v>
+        <v>-2.4731</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1346</v>
+        <v>2.1313</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.6062</v>
+        <v>-4.6045</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8791</v>
+        <v>0.8659</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9228</v>
+        <v>3.9128</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.0438</v>
+        <v>-3.0469</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3507</v>
+        <v>-3.339</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7883</v>
+        <v>-1.7814</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5625</v>
+        <v>-1.5576</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3372</v>
+        <v>-0.5285</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5363</v>
+        <v>0.0531</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.5816</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6035</v>
+        <v>-7.0423</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3466</v>
+        <v>-3.0268</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2569</v>
+        <v>-4.0154</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5347</v>
+        <v>-2.5388</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6515</v>
+        <v>0.6443</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.1862</v>
+        <v>-3.1831</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1247</v>
+        <v>0.1107</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5907</v>
+        <v>1.5783</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.466</v>
+        <v>-1.4676</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6595</v>
+        <v>-2.6496</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9392</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>1.0625</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3227</v>
+        <v>0.6639</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1772</v>
+        <v>0.3986</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.2056</v>
+        <v>-4.2001</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.8194</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.7376</v>
+        <v>2.735399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0813</v>
+        <v>15.913</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.3436</v>
+        <v>-13.1775</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2575</v>
+        <v>-3.27</v>
       </c>
       <c r="H25" t="n">
-        <v>7.1381</v>
+        <v>7.111300000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.3954</v>
+        <v>-10.3815</v>
       </c>
       <c r="J25" t="n">
-        <v>17.9563</v>
+        <v>17.8504</v>
       </c>
       <c r="K25" t="n">
-        <v>14.8772</v>
+        <v>14.8005</v>
       </c>
       <c r="L25" t="n">
-        <v>3.078899999999999</v>
+        <v>3.0501</v>
       </c>
       <c r="M25" t="n">
-        <v>-21.2135</v>
+        <v>-21.1205</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.739099999999999</v>
+        <v>-7.688899999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-13.4745</v>
+        <v>-13.4315</v>
       </c>
       <c r="P25" t="n">
-        <v>6.815499999999999</v>
+        <v>6.828899999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-10.2233</v>
+        <v>-10.2436</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0391</v>
+        <v>17.0724</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8838000000000001</v>
+        <v>0.8824000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3901</v>
+        <v>1.3673</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5065999999999999</v>
+        <v>-0.4849999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.704199999999999</v>
+        <v>-1.7055</v>
       </c>
       <c r="W25" t="n">
-        <v>6.958500000000001</v>
+        <v>6.938599999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.662799999999999</v>
+        <v>-8.644400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104732_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104732_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>1.0032</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.9386</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104732_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.644400000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
